--- a/SGC-CKN/Excel/0f9d5b23-e77b-432a-8200-6a8465ea682a_Lô_CT-02_P1-72_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/0f9d5b23-e77b-432a-8200-6a8465ea682a_Lô_CT-02_P1-72_D800_31-03-2026.xlsx
@@ -1145,7 +1145,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.18</v>
@@ -1157,7 +1157,7 @@
         <v>1.18</v>
       </c>
       <c r="J11" s="8">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1557,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.18</v>
@@ -1789,7 +1789,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.5</v>
